--- a/results/Real Dateset WGS T2D/Real Dateset WGS T2D AUROC.xlsx
+++ b/results/Real Dateset WGS T2D/Real Dateset WGS T2D AUROC.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14568" windowHeight="9684"/>
+    <workbookView windowWidth="18180" windowHeight="9912"/>
   </bookViews>
   <sheets>
     <sheet name="model_1_detailed_results" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Fold</t>
   </si>
@@ -36,9 +36,6 @@
   </si>
   <si>
     <t>Pred Score</t>
-  </si>
-  <si>
-    <t>Predicted Label</t>
   </si>
 </sst>
 </file>
@@ -1200,13 +1197,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D110"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:C110"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="11.7777777777778"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1216,11 +1213,8 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1230,11 +1224,8 @@
       <c r="C2">
         <v>0.58927727</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1244,11 +1235,8 @@
       <c r="C3">
         <v>0.5051559</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1258,11 +1246,8 @@
       <c r="C4">
         <v>0.33604518</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1272,11 +1257,8 @@
       <c r="C5">
         <v>0.38014373</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1286,11 +1268,8 @@
       <c r="C6">
         <v>0.19630949</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1300,11 +1279,8 @@
       <c r="C7">
         <v>0.67173606</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1314,11 +1290,8 @@
       <c r="C8">
         <v>0.7017817</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1328,11 +1301,8 @@
       <c r="C9">
         <v>0.75471663</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1342,11 +1312,8 @@
       <c r="C10">
         <v>0.61021036</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1356,11 +1323,8 @@
       <c r="C11">
         <v>0.5088604</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1370,11 +1334,8 @@
       <c r="C12">
         <v>0.72635686</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1384,11 +1345,8 @@
       <c r="C13">
         <v>0.53604317</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1398,11 +1356,8 @@
       <c r="C14">
         <v>0.61900216</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -1412,11 +1367,8 @@
       <c r="C15">
         <v>0.58389175</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1426,11 +1378,8 @@
       <c r="C16">
         <v>0.585162</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1440,11 +1389,8 @@
       <c r="C17">
         <v>0.30750126</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1454,11 +1400,8 @@
       <c r="C18">
         <v>0.42857906</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -1468,11 +1411,8 @@
       <c r="C19">
         <v>0.6199939</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -1482,11 +1422,8 @@
       <c r="C20">
         <v>0.4646552</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -1496,11 +1433,8 @@
       <c r="C21">
         <v>0.328486</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -1510,11 +1444,8 @@
       <c r="C22">
         <v>0.58114994</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>1</v>
       </c>
@@ -1524,11 +1455,8 @@
       <c r="C23">
         <v>0.26845106</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>2</v>
       </c>
@@ -1538,11 +1466,8 @@
       <c r="C24">
         <v>0.4006392</v>
       </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>2</v>
       </c>
@@ -1552,11 +1477,8 @@
       <c r="C25">
         <v>0.801749</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>2</v>
       </c>
@@ -1566,11 +1488,8 @@
       <c r="C26">
         <v>0.3854285</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>2</v>
       </c>
@@ -1580,11 +1499,8 @@
       <c r="C27">
         <v>0.4890854</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>2</v>
       </c>
@@ -1594,11 +1510,8 @@
       <c r="C28">
         <v>0.652591</v>
       </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>2</v>
       </c>
@@ -1608,11 +1521,8 @@
       <c r="C29">
         <v>0.8682811</v>
       </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>2</v>
       </c>
@@ -1622,11 +1532,8 @@
       <c r="C30">
         <v>0.3767826</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>2</v>
       </c>
@@ -1636,11 +1543,8 @@
       <c r="C31">
         <v>0.44965038</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>2</v>
       </c>
@@ -1650,11 +1554,8 @@
       <c r="C32">
         <v>0.90484947</v>
       </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>2</v>
       </c>
@@ -1664,11 +1565,8 @@
       <c r="C33">
         <v>0.69637704</v>
       </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>2</v>
       </c>
@@ -1678,11 +1576,8 @@
       <c r="C34">
         <v>0.9999995</v>
       </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>2</v>
       </c>
@@ -1692,11 +1587,8 @@
       <c r="C35">
         <v>0.5265029</v>
       </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>2</v>
       </c>
@@ -1706,11 +1598,8 @@
       <c r="C36">
         <v>0.6169231</v>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>2</v>
       </c>
@@ -1720,11 +1609,8 @@
       <c r="C37">
         <v>0.61238754</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>2</v>
       </c>
@@ -1734,11 +1620,8 @@
       <c r="C38">
         <v>0.5409787</v>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>2</v>
       </c>
@@ -1748,11 +1631,8 @@
       <c r="C39">
         <v>0.7574038</v>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>2</v>
       </c>
@@ -1762,11 +1642,8 @@
       <c r="C40">
         <v>0.6558968</v>
       </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>2</v>
       </c>
@@ -1776,11 +1653,8 @@
       <c r="C41">
         <v>0.7408245</v>
       </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>2</v>
       </c>
@@ -1790,11 +1664,8 @@
       <c r="C42">
         <v>0.7159771</v>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>2</v>
       </c>
@@ -1804,11 +1675,8 @@
       <c r="C43">
         <v>0.64295727</v>
       </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>2</v>
       </c>
@@ -1818,11 +1686,8 @@
       <c r="C44">
         <v>0.42338216</v>
       </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>2</v>
       </c>
@@ -1832,11 +1697,8 @@
       <c r="C45">
         <v>0.032123</v>
       </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>3</v>
       </c>
@@ -1846,11 +1708,8 @@
       <c r="C46">
         <v>0.39249995</v>
       </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>3</v>
       </c>
@@ -1860,11 +1719,8 @@
       <c r="C47">
         <v>0.56457675</v>
       </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>3</v>
       </c>
@@ -1874,11 +1730,8 @@
       <c r="C48">
         <v>0.5729936</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>3</v>
       </c>
@@ -1888,11 +1741,8 @@
       <c r="C49">
         <v>0.37053668</v>
       </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>3</v>
       </c>
@@ -1902,11 +1752,8 @@
       <c r="C50">
         <v>0.3885481</v>
       </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>3</v>
       </c>
@@ -1916,11 +1763,8 @@
       <c r="C51">
         <v>0.4308282</v>
       </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
@@ -1930,11 +1774,8 @@
       <c r="C52">
         <v>0.4725164</v>
       </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>3</v>
       </c>
@@ -1944,11 +1785,8 @@
       <c r="C53">
         <v>0.6405218</v>
       </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
@@ -1958,11 +1796,8 @@
       <c r="C54">
         <v>0.6519315</v>
       </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>3</v>
       </c>
@@ -1972,11 +1807,8 @@
       <c r="C55">
         <v>0.57952446</v>
       </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>3</v>
       </c>
@@ -1986,11 +1818,8 @@
       <c r="C56">
         <v>0.6594293</v>
       </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>3</v>
       </c>
@@ -2000,11 +1829,8 @@
       <c r="C57">
         <v>0.6852508</v>
       </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>3</v>
       </c>
@@ -2014,11 +1840,8 @@
       <c r="C58">
         <v>0.6404808</v>
       </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>3</v>
       </c>
@@ -2028,11 +1851,8 @@
       <c r="C59">
         <v>0.3788211</v>
       </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>3</v>
       </c>
@@ -2042,11 +1862,8 @@
       <c r="C60">
         <v>0.46954715</v>
       </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>3</v>
       </c>
@@ -2056,11 +1873,8 @@
       <c r="C61">
         <v>0.7201593</v>
       </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>3</v>
       </c>
@@ -2070,11 +1884,8 @@
       <c r="C62">
         <v>0.5868332</v>
       </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>3</v>
       </c>
@@ -2084,11 +1895,8 @@
       <c r="C63">
         <v>0.1801563</v>
       </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>3</v>
       </c>
@@ -2098,11 +1906,8 @@
       <c r="C64">
         <v>0.28144625</v>
       </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>3</v>
       </c>
@@ -2112,11 +1917,8 @@
       <c r="C65">
         <v>0.2748098</v>
       </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>3</v>
       </c>
@@ -2126,11 +1928,8 @@
       <c r="C66">
         <v>0.24443245</v>
       </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>3</v>
       </c>
@@ -2140,11 +1939,8 @@
       <c r="C67">
         <v>0.20156583</v>
       </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>4</v>
       </c>
@@ -2154,11 +1950,8 @@
       <c r="C68">
         <v>0.6021756</v>
       </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>4</v>
       </c>
@@ -2168,11 +1961,8 @@
       <c r="C69">
         <v>0.31041017</v>
       </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>4</v>
       </c>
@@ -2182,11 +1972,8 @@
       <c r="C70">
         <v>0.38987267</v>
       </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>4</v>
       </c>
@@ -2196,11 +1983,8 @@
       <c r="C71">
         <v>0.5107949</v>
       </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>4</v>
       </c>
@@ -2210,11 +1994,8 @@
       <c r="C72">
         <v>0.48894522</v>
       </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73">
         <v>4</v>
       </c>
@@ -2224,11 +2005,8 @@
       <c r="C73">
         <v>0.5124995</v>
       </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>4</v>
       </c>
@@ -2238,11 +2016,8 @@
       <c r="C74">
         <v>0.612391</v>
       </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
         <v>4</v>
       </c>
@@ -2252,11 +2027,8 @@
       <c r="C75">
         <v>0.4453785</v>
       </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>4</v>
       </c>
@@ -2266,11 +2038,8 @@
       <c r="C76">
         <v>0.3632181</v>
       </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>4</v>
       </c>
@@ -2280,11 +2049,8 @@
       <c r="C77">
         <v>0.46452603</v>
       </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
         <v>4</v>
       </c>
@@ -2294,11 +2060,8 @@
       <c r="C78">
         <v>0.49327657</v>
       </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>4</v>
       </c>
@@ -2308,11 +2071,8 @@
       <c r="C79">
         <v>0.5730761</v>
       </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>4</v>
       </c>
@@ -2322,11 +2082,8 @@
       <c r="C80">
         <v>0.5627009</v>
       </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
         <v>4</v>
       </c>
@@ -2336,11 +2093,8 @@
       <c r="C81">
         <v>0.49544305</v>
       </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
         <v>4</v>
       </c>
@@ -2350,11 +2104,8 @@
       <c r="C82">
         <v>0.57835895</v>
       </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
         <v>4</v>
       </c>
@@ -2364,11 +2115,8 @@
       <c r="C83">
         <v>0.39395565</v>
       </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84">
         <v>4</v>
       </c>
@@ -2378,11 +2126,8 @@
       <c r="C84">
         <v>0.7759818</v>
       </c>
-      <c r="D84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85">
         <v>4</v>
       </c>
@@ -2392,11 +2137,8 @@
       <c r="C85">
         <v>0.483505</v>
       </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86">
         <v>4</v>
       </c>
@@ -2406,11 +2148,8 @@
       <c r="C86">
         <v>0.24198018</v>
       </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87">
         <v>4</v>
       </c>
@@ -2420,11 +2159,8 @@
       <c r="C87">
         <v>0.30284825</v>
       </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88">
         <v>4</v>
       </c>
@@ -2434,11 +2170,8 @@
       <c r="C88">
         <v>0.40229666</v>
       </c>
-      <c r="D88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89">
         <v>4</v>
       </c>
@@ -2448,11 +2181,8 @@
       <c r="C89">
         <v>0.5108657</v>
       </c>
-      <c r="D89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90">
         <v>5</v>
       </c>
@@ -2462,11 +2192,8 @@
       <c r="C90">
         <v>0.38998145</v>
       </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91">
         <v>5</v>
       </c>
@@ -2476,11 +2203,8 @@
       <c r="C91">
         <v>0.5431817</v>
       </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92">
         <v>5</v>
       </c>
@@ -2490,11 +2214,8 @@
       <c r="C92">
         <v>0.6688101</v>
       </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93">
         <v>5</v>
       </c>
@@ -2504,11 +2225,8 @@
       <c r="C93">
         <v>0.38244674</v>
       </c>
-      <c r="D93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94">
         <v>5</v>
       </c>
@@ -2518,11 +2236,8 @@
       <c r="C94">
         <v>0.76824284</v>
       </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95">
         <v>5</v>
       </c>
@@ -2532,11 +2247,8 @@
       <c r="C95">
         <v>0.8475623</v>
       </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96">
         <v>5</v>
       </c>
@@ -2546,11 +2258,8 @@
       <c r="C96">
         <v>0.50791186</v>
       </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <v>5</v>
       </c>
@@ -2560,11 +2269,8 @@
       <c r="C97">
         <v>0.44948465</v>
       </c>
-      <c r="D97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <v>5</v>
       </c>
@@ -2574,11 +2280,8 @@
       <c r="C98">
         <v>0.47379047</v>
       </c>
-      <c r="D98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
         <v>5</v>
       </c>
@@ -2588,11 +2291,8 @@
       <c r="C99">
         <v>0.7249447</v>
       </c>
-      <c r="D99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
         <v>5</v>
       </c>
@@ -2602,11 +2302,8 @@
       <c r="C100">
         <v>0.78791934</v>
       </c>
-      <c r="D100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
         <v>5</v>
       </c>
@@ -2616,11 +2313,8 @@
       <c r="C101">
         <v>0.54495853</v>
       </c>
-      <c r="D101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102">
         <v>5</v>
       </c>
@@ -2630,11 +2324,8 @@
       <c r="C102">
         <v>0.6916939</v>
       </c>
-      <c r="D102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103">
         <v>5</v>
       </c>
@@ -2644,11 +2335,8 @@
       <c r="C103">
         <v>0.67990094</v>
       </c>
-      <c r="D103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+    </row>
+    <row r="104" spans="1:3">
       <c r="A104">
         <v>5</v>
       </c>
@@ -2658,11 +2346,8 @@
       <c r="C104">
         <v>0.7757518</v>
       </c>
-      <c r="D104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+    </row>
+    <row r="105" spans="1:3">
       <c r="A105">
         <v>5</v>
       </c>
@@ -2672,11 +2357,8 @@
       <c r="C105">
         <v>0.40039337</v>
       </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+    </row>
+    <row r="106" spans="1:3">
       <c r="A106">
         <v>5</v>
       </c>
@@ -2686,11 +2368,8 @@
       <c r="C106">
         <v>0.7173013</v>
       </c>
-      <c r="D106">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107">
         <v>5</v>
       </c>
@@ -2700,11 +2379,8 @@
       <c r="C107">
         <v>0.5267458</v>
       </c>
-      <c r="D107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
+    </row>
+    <row r="108" spans="1:3">
       <c r="A108">
         <v>5</v>
       </c>
@@ -2714,11 +2390,8 @@
       <c r="C108">
         <v>0.20212777</v>
       </c>
-      <c r="D108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
+    </row>
+    <row r="109" spans="1:3">
       <c r="A109">
         <v>5</v>
       </c>
@@ -2728,11 +2401,8 @@
       <c r="C109">
         <v>0.00010012</v>
       </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
+    </row>
+    <row r="110" spans="1:3">
       <c r="A110">
         <v>5</v>
       </c>
@@ -2741,9 +2411,6 @@
       </c>
       <c r="C110">
         <v>0.3761092</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
